--- a/education_forms/023_osce_evaluation_form--education_forms.xlsx
+++ b/education_forms/023_osce_evaluation_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide a brief introduction to this OSCE evaluation form.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,38 +547,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>osce_station</t>
+          <t>osce_satisfaction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>osce_station</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Satisfaction with OSCE program</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rate your level of satisfaction with the OSCE program</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>osce_station_id</t>
+          <t>osce_experience</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>osce_station</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Overall experience with OSCE program</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Rate your overall experience with the OSCE program</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>osce_station</t>
+          <t>osce_likes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>osce_station</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What did you like most about OSCE program</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please provide your reasons for liking the OSCE program</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>osce_station</t>
+          <t>osce_dislikes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>osce_station</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What did you like least about OSCE program</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide your reasons for disliking the OSCE program</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,18 +655,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>osce_station</t>
+          <t>osce_teaching</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>osce_station</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>OSCE teaching quality</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Rate the quality of teaching in the OSCE program</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +682,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>osce_station_id</t>
+          <t>osce_expectations</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>osce_station</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Expectations for OSCE program future</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please provide your expectations for the OSCE program in the future</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>page_2</t>
+          <t>osce_improvements</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>evaluation</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Recommendations for OSCE program improvements</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide your suggestions for improving the OSCE program</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,43 +731,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>osce_value</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>evaluation</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>OSCE program value</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rate the value of the OSCE program</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>osce_relevance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>evaluation</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>OSCE program relevance</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Rate the relevance of the OSCE program to your field of practice</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>osce_suggestions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>evaluation</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Suggestions for OSCE program development</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide your suggestions for developing the OSCE program</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,85 +817,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>page_3</t>
+          <t>osce_final_thoughts</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>conclusion</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Final thoughts and comments</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please provide any final thoughts or comments about the OSCE program</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>osce_station</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>osce_station</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>osce_station_id</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>osce_station</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>page_4</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -896,340 +875,323 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>osce_station_choices</t>
+          <t>osce_satisfaction_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>osce_station_choices</t>
+          <t>osce_satisfaction_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>osce_station_choices</t>
+          <t>osce_satisfaction_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>osce_station_choices</t>
+          <t>osce_satisfaction_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>osce_station_choices</t>
+          <t>osce_satisfaction_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>osce_station_choices</t>
+          <t>osce_experience_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>osce_station_choices</t>
+          <t>osce_experience_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>osce_station_choices</t>
+          <t>osce_experience_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>osce_station_choices</t>
+          <t>osce_experience_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>osce_station_choices</t>
+          <t>osce_teaching_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>osce_station_choices</t>
+          <t>osce_teaching_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>osce_teaching_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>osce_teaching_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>osce_value_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>osce_value_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>osce_station_choices</t>
+          <t>osce_value_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>osce_station_choices</t>
+          <t>osce_relevance_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>osce_station_choices</t>
+          <t>osce_relevance_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>osce_station_choices</t>
+          <t>osce_relevance_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>osce_station_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
